--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104571_W13.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104571_W13.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1753</v>
+        <v>4.7723</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6853</v>
+        <v>3.5675</v>
       </c>
       <c r="F2" t="n">
-        <v>1.49</v>
+        <v>1.2048</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4272</v>
+        <v>3.4293</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8354</v>
+        <v>2.8348</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5918</v>
+        <v>0.5945</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6875</v>
+        <v>3.6722</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9785</v>
+        <v>2.9647</v>
       </c>
       <c r="L2" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2603</v>
+        <v>-0.243</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7501</v>
+        <v>0.3414</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0393</v>
+        <v>-0.0561</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7107</v>
+        <v>0.3975</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9965</v>
+        <v>2.738</v>
       </c>
       <c r="E3" t="n">
-        <v>3.317</v>
+        <v>3.0015</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3205</v>
+        <v>-0.2635</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7454</v>
+        <v>1.7439</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5801</v>
+        <v>1.5769</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1653</v>
+        <v>0.1669</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3438</v>
+        <v>2.3156</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7867</v>
+        <v>1.7647</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5984</v>
+        <v>-0.5717</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2066</v>
+        <v>-0.1877</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5901</v>
+        <v>-0.8466</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2662</v>
+        <v>-0.0166</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8562</v>
+        <v>-0.83</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1891</v>
+        <v>0.8504</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8619</v>
+        <v>1.3886</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6728</v>
+        <v>-0.5381</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0694</v>
+        <v>1.0781</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1124</v>
+        <v>0.1202</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9569</v>
+        <v>0.9579</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2661</v>
+        <v>1.2633</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2315</v>
+        <v>1.2288</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1967</v>
+        <v>-0.1852</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1071</v>
+        <v>-0.4553</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5958</v>
+        <v>0.1253</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7029</v>
+        <v>-0.5805</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. CATE</t>
+          <t>Z. HICKS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3581</v>
+        <v>0.0244</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5785</v>
+        <v>1.0035</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.2204</v>
+        <v>-0.9791</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4471</v>
+        <v>-0.4295</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6682</v>
+        <v>-0.1728</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2212</v>
+        <v>-0.2567</v>
       </c>
       <c r="J5" t="n">
-        <v>0.766</v>
+        <v>0.1004</v>
       </c>
       <c r="K5" t="n">
-        <v>0.654</v>
+        <v>0.0862</v>
       </c>
       <c r="L5" t="n">
-        <v>0.112</v>
+        <v>0.0142</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3189</v>
+        <v>-0.53</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0142</v>
+        <v>-0.259</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3331</v>
+        <v>-0.271</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4793</v>
+        <v>1.4075</v>
       </c>
       <c r="T5" t="n">
-        <v>3.3057</v>
+        <v>0.9729</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1736</v>
+        <v>0.4345</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.6609</v>
+        <v>-1.1812</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8678</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.5287</v>
+        <v>-1.3389</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Z. HICKS</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1993</v>
+        <v>0.0068</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1355</v>
+        <v>1.2162</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9361</v>
+        <v>-1.2094</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4273</v>
+        <v>0.7254</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.182</v>
+        <v>1.0426</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2453</v>
+        <v>-0.3172</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1158</v>
+        <v>1.1976</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0866</v>
+        <v>1.0859</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0292</v>
+        <v>0.1117</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5431</v>
+        <v>-0.4722</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2685</v>
+        <v>-0.0433</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2745</v>
+        <v>-0.4289</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5824</v>
+        <v>-0.5609</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0858</v>
+        <v>0.0185</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4966</v>
+        <v>-0.5794</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1826</v>
+        <v>-0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3433</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0274</v>
+        <v>-0.5588</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2211</v>
+        <v>-0.7438</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2484</v>
+        <v>0.185</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7234</v>
+        <v>-0.9176</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0433</v>
+        <v>-0.368</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3198</v>
+        <v>-0.5496</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2029</v>
+        <v>-0.3459</v>
       </c>
       <c r="K7" t="n">
-        <v>1.091</v>
+        <v>-0.3382</v>
       </c>
       <c r="L7" t="n">
-        <v>0.112</v>
+        <v>-0.0077</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4795</v>
+        <v>-0.5717</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0477</v>
+        <v>-0.0298</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4318</v>
+        <v>-0.5419</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5901</v>
+        <v>0.9952</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0181</v>
+        <v>0.8101</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6082</v>
+        <v>0.1851</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1607</v>
+        <v>-0.6364</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>-0.7942</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>J. RADEBAUGH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6031</v>
+        <v>-1.1616</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9119</v>
+        <v>-0.1509</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3088</v>
+        <v>-1.0108</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.927</v>
+        <v>0.7373</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3753</v>
+        <v>-0.2012</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5517</v>
+        <v>0.9386</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3286</v>
+        <v>1.3383</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3259</v>
+        <v>0.0722</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0027</v>
+        <v>1.2661</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5984</v>
+        <v>-0.6009</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0494</v>
+        <v>-0.2734</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.549</v>
+        <v>-0.3275</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9603</v>
+        <v>-0.3542</v>
       </c>
       <c r="T8" t="n">
-        <v>0.617</v>
+        <v>-0.351</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3433</v>
+        <v>-0.0033</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6363</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.797</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. RADEBAUGH</t>
+          <t>E. CATE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7076</v>
+        <v>-1.6531</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3938</v>
+        <v>1.6622</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3138</v>
+        <v>-3.3153</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7307</v>
+        <v>0.4425</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.205</v>
+        <v>0.6583</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9356</v>
+        <v>-0.2158</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3482</v>
+        <v>0.742</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0795</v>
+        <v>0.6303</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2688</v>
+        <v>0.1117</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6176</v>
+        <v>-0.2995</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2844</v>
+        <v>0.028</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4537</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8919</v>
+        <v>1.4725</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6079</v>
+        <v>1.4257</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.284</v>
+        <v>0.0468</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>-2.6576</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.8603</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-3.5179</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4897</v>
+        <v>-3.3089</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.578</v>
+        <v>-1.7407</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0883</v>
+        <v>-1.5682</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2024</v>
+        <v>0.3423</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6061</v>
+        <v>-0.9932</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.5963</v>
+        <v>1.3355</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.0215</v>
+        <v>0.8983</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6998</v>
+        <v>-1.1936</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.3218</v>
+        <v>2.0918</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1808</v>
+        <v>-0.556</v>
       </c>
       <c r="N10" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.2003</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2745</v>
+        <v>-0.7563</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2589</v>
+        <v>-0.4912</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5565</v>
+        <v>-0.135</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2976</v>
+        <v>-0.3562</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.4822</v>
+        <v>-1.3389</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.4822</v>
+        <v>-1.3389</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9221</v>
+        <v>-3.3517</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2973</v>
+        <v>-3.3349</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6248</v>
+        <v>-0.0167</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3673</v>
+        <v>-3.2059</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9839</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3513</v>
+        <v>-2.6026</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9449</v>
+        <v>-3.0351</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1713</v>
+        <v>-0.7035</v>
       </c>
       <c r="L11" t="n">
-        <v>2.1162</v>
+        <v>-2.3317</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5776</v>
+        <v>-0.1708</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1874</v>
+        <v>0.1002</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7649</v>
+        <v>-0.271</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1314</v>
+        <v>-0.1277</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.747</v>
+        <v>-0.2998</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3844</v>
+        <v>0.1721</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.3433</v>
+        <v>-0.4733</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.3433</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. DEJULIUS</t>
+          <t>D. ENNIS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0138</v>
+        <v>-4.766</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.5042</v>
+        <v>-2.4073</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-2.3586</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.404</v>
+        <v>-1.1874</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.0764</v>
+        <v>-0.9653</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3276</v>
+        <v>-0.2221</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.9229</v>
+        <v>-0.7736</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.7125</v>
+        <v>-1.0934</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2104</v>
+        <v>0.3198</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4812</v>
+        <v>-0.4138</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3639</v>
+        <v>0.1281</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1172</v>
+        <v>-0.5419</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-2.5039</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6778</v>
+        <v>-0.0999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6079</v>
+        <v>0.5547</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0699</v>
+        <v>-0.6546</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-2.1129</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0.3155</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-2.4284</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. ENNIS</t>
+          <t>D. DEJULIUS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.3116</v>
+        <v>-5.0572</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6679</v>
+        <v>-4.6069</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6437</v>
+        <v>-0.4503</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.1883</v>
+        <v>-4.4239</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9697</v>
+        <v>-3.0733</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2186</v>
+        <v>-1.3506</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7472</v>
+        <v>-3.9652</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.0776</v>
+        <v>-2.7276</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3304</v>
+        <v>-1.2376</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4411</v>
+        <v>-0.4587</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1079</v>
+        <v>-0.3457</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.549</v>
+        <v>-0.113</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.4952</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6477</v>
+        <v>0.2984</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.747</v>
+        <v>0.3388</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.0403</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.1146</v>
+        <v>-0.9317</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3214</v>
+        <v>0.1578</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.436</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-12.157</v>
+        <v>-11.4654</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.553799999999999</v>
+        <v>-1.145</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.603</v>
+        <v>-10.3202</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.6385</v>
+        <v>-1.6655</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1590000000000007</v>
+        <v>-0.1442999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.4796</v>
+        <v>-1.5212</v>
       </c>
       <c r="J14" t="n">
-        <v>3.655000000000001</v>
+        <v>3.407900000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7237999999999998</v>
+        <v>0.5822000000000003</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9312</v>
+        <v>2.8255</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.2936</v>
+        <v>-5.073500000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.7266</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.410600000000001</v>
+        <v>-4.347</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.2684</v>
+        <v>-2.2764</v>
       </c>
       <c r="Q14" t="n">
-        <v>-11.3418</v>
+        <v>-11.3816</v>
       </c>
       <c r="R14" t="n">
-        <v>9.073499999999999</v>
+        <v>9.105499999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8771000000000004</v>
+        <v>1.5792</v>
       </c>
       <c r="T14" t="n">
-        <v>2.661600000000001</v>
+        <v>3.3875</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.7845</v>
+        <v>-1.8083</v>
       </c>
       <c r="V14" t="n">
-        <v>-9.127000000000001</v>
+        <v>-9.102899999999998</v>
       </c>
       <c r="W14" t="n">
-        <v>3.4711</v>
+        <v>3.4412</v>
       </c>
       <c r="X14" t="n">
-        <v>-12.598</v>
+        <v>-12.5439</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.86</v>
+        <v>5.2736</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1519</v>
+        <v>5.0572</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2919</v>
+        <v>0.2164</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1059</v>
+        <v>2.6785</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5382</v>
+        <v>0.9271</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6442</v>
+        <v>1.7514</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1126</v>
+        <v>2.7171</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3912</v>
+        <v>0.4686</v>
       </c>
       <c r="L15" t="n">
-        <v>2.7214</v>
+        <v>2.2484</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0066</v>
+        <v>-0.0386</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9294</v>
+        <v>0.4584</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0772</v>
+        <v>-0.497</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1342</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6199</v>
+        <v>-1.0603</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9467</v>
+        <v>-0.1072</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6732</v>
+        <v>-0.9530999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>3.6554</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>3.8132</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1985</v>
+        <v>4.2469</v>
       </c>
       <c r="E16" t="n">
-        <v>4.3927</v>
+        <v>4.5423</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1942</v>
+        <v>-0.2954</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6753</v>
+        <v>2.1054</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9161</v>
+        <v>-0.5371</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7592</v>
+        <v>2.6425</v>
       </c>
       <c r="J16" t="n">
-        <v>2.746</v>
+        <v>3.0931</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4778</v>
+        <v>0.3825</v>
       </c>
       <c r="L16" t="n">
-        <v>2.2682</v>
+        <v>2.7106</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0707</v>
+        <v>-0.9877</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4383</v>
+        <v>-0.9196</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.509</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.1404</v>
+        <v>1.0034</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8166</v>
+        <v>0.3597</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.3238</v>
+        <v>0.6437</v>
       </c>
       <c r="V16" t="n">
-        <v>3.6636</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.8243</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.4762</v>
+        <v>3.2658</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8354</v>
+        <v>2.3521</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6408</v>
+        <v>0.9137</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0016</v>
+        <v>1.0033</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9105</v>
+        <v>1.9072</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9089</v>
+        <v>-0.904</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8192</v>
+        <v>1.8042</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4936</v>
+        <v>2.4821</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8176</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1817</v>
+        <v>0.965</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0162</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1654</v>
+        <v>0.4171</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2272</v>
+        <v>2.105</v>
       </c>
       <c r="E18" t="n">
-        <v>0.776</v>
+        <v>0.8809</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4513</v>
+        <v>1.2241</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1527</v>
+        <v>1.16</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0966</v>
+        <v>1.0971</v>
       </c>
       <c r="I18" t="n">
-        <v>0.056</v>
+        <v>0.0629</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4485</v>
+        <v>0.4397</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3739</v>
+        <v>0.3652</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7042</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7228</v>
+        <v>0.7319</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5359</v>
+        <v>-0.6712</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5383</v>
+        <v>-0.4207</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0024</v>
+        <v>-0.2505</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1568</v>
+        <v>1.1609</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.8476</v>
+        <v>1.7783</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5322</v>
+        <v>1.2784</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3153</v>
+        <v>0.4999</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2003</v>
+        <v>2.2089</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6752</v>
+        <v>1.6799</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5251</v>
+        <v>0.529</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6502</v>
+        <v>1.6318</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2051</v>
+        <v>1.1926</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5502</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4701</v>
+        <v>0.4873</v>
       </c>
       <c r="O19" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0994</v>
+        <v>-1.1834</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1089</v>
+        <v>-0.1258</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.2083</v>
+        <v>-1.0576</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3089</v>
+        <v>0.4394</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2681</v>
+        <v>0.1257</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0408</v>
+        <v>0.3137</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6623</v>
+        <v>-0.6585</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0995</v>
+        <v>-1.1027</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4372</v>
+        <v>0.4442</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0179</v>
+        <v>-0.0299</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6896</v>
+        <v>-0.7002</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6444</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5344</v>
+        <v>0.6701</v>
       </c>
       <c r="T20" t="n">
-        <v>0.369</v>
+        <v>0.253</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1654</v>
+        <v>0.4171</v>
       </c>
       <c r="V20" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1136</v>
+        <v>0.1537</v>
       </c>
       <c r="E21" t="n">
-        <v>2.183</v>
+        <v>-0.6536</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2966</v>
+        <v>0.8073</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9221</v>
+        <v>-0.968</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6636</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2585</v>
+        <v>-0.3647</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1313</v>
+        <v>0.0762</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.206</v>
+        <v>0.1584</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0746</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-1.0442</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4576</v>
+        <v>-0.7617</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3331</v>
+        <v>-0.2826</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8745</v>
+        <v>0.9639</v>
       </c>
       <c r="T21" t="n">
-        <v>1.9417</v>
+        <v>0.2505</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0672</v>
+        <v>0.7134</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W21" t="n">
-        <v>2.5068</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.3461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7658</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7756999999999999</v>
+        <v>-0.4512</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01</v>
+        <v>0.3826</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5602</v>
+        <v>-0.5614</v>
       </c>
       <c r="H22" t="n">
-        <v>1.127</v>
+        <v>1.1232</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6873</v>
+        <v>-1.6846</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8782</v>
+        <v>0.8552</v>
       </c>
       <c r="K22" t="n">
-        <v>1.7419</v>
+        <v>1.7269</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.8637</v>
+        <v>-0.8718</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4384</v>
+        <v>-1.4166</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.405</v>
+        <v>1.109</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0907</v>
+        <v>0.448</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3142</v>
+        <v>0.6611</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0191</v>
+        <v>-0.9255</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5803</v>
+        <v>-1.6252</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5613</v>
+        <v>0.6997</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9765</v>
+        <v>-0.0497</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6061</v>
+        <v>-0.1691</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3705</v>
+        <v>0.1194</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0887</v>
+        <v>-0.7572</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1661</v>
+        <v>-1.1591</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.4019</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0653</v>
+        <v>0.7074</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7721</v>
+        <v>0.99</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2032</v>
+        <v>-1.1717</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6956</v>
+        <v>-0.2535</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4924</v>
+        <v>-0.9182</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1607</v>
+        <v>-0.387</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>-0.387</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4006</v>
+        <v>-1.2524</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2312</v>
+        <v>-2.2735</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8306</v>
+        <v>1.0211</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3278</v>
+        <v>-3.3259</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.4962</v>
+        <v>-2.504</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8316</v>
+        <v>-0.8218</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.5716</v>
+        <v>-3.6032</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.9345</v>
+        <v>-2.9625</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2439</v>
+        <v>0.2773</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4383</v>
+        <v>0.4584</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8045</v>
+        <v>-0.6502</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0302</v>
+        <v>-0.0283</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7743</v>
+        <v>-0.622</v>
       </c>
       <c r="V24" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W24" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.4625</v>
+        <v>-1.2743</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.9493</v>
+        <v>1.0874</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4867</v>
+        <v>-2.3618</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0483</v>
+        <v>-1.9268</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.163</v>
+        <v>-1.6739</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1147</v>
+        <v>-0.253</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.7289</v>
+        <v>-1.1536</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.1367</v>
+        <v>-1.228</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4078</v>
+        <v>0.0745</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6806</v>
+        <v>-0.7733</v>
       </c>
       <c r="N25" t="n">
-        <v>0.9737</v>
+        <v>-0.4458</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2931</v>
+        <v>-0.3275</v>
       </c>
       <c r="P25" t="n">
-        <v>0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7091</v>
+        <v>0.7224</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6079</v>
+        <v>0.8847</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.1012</v>
+        <v>-0.1623</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3856</v>
+        <v>0.1578</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.3856</v>
+        <v>2.4945</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>12.1568</v>
+        <v>13.7419</v>
       </c>
       <c r="E26" t="n">
-        <v>10.6028</v>
+        <v>10.3205</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5541</v>
+        <v>3.421299999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>1.638600000000001</v>
+        <v>1.665800000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1588000000000001</v>
+        <v>0.1443999999999994</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4796</v>
+        <v>1.5213</v>
       </c>
       <c r="J26" t="n">
-        <v>5.2937</v>
+        <v>5.073399999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8827999999999998</v>
+        <v>0.7264999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>4.4109</v>
+        <v>4.3469</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.654899999999999</v>
+        <v>-3.4077</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.7237999999999998</v>
+        <v>-0.5822000000000003</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.9312</v>
+        <v>-2.8256</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2684</v>
+        <v>2.2764</v>
       </c>
       <c r="Q26" t="n">
-        <v>-9.073300000000001</v>
+        <v>-9.1053</v>
       </c>
       <c r="R26" t="n">
-        <v>11.3417</v>
+        <v>11.3817</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8770000000000002</v>
+        <v>0.6969999999999996</v>
       </c>
       <c r="T26" t="n">
-        <v>1.7846</v>
+        <v>1.8083</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.6618</v>
+        <v>-1.1113</v>
       </c>
       <c r="V26" t="n">
-        <v>9.126900000000001</v>
+        <v>9.1028</v>
       </c>
       <c r="W26" t="n">
-        <v>12.5981</v>
+        <v>12.5439</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.4711</v>
+        <v>-3.4412</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104571_W13.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104571_W13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.3389</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.7942</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-3.5179</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.3389</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.4284</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-12.5439</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104571_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-3.4412</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
